--- a/dcf/AMAT.xlsx
+++ b/dcf/AMAT.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1105,25 +1105,25 @@
         </is>
       </c>
       <c r="B4" s="52" t="n">
-        <v>0.1067182049427388</v>
+        <v>0.1066340473844373</v>
       </c>
       <c r="C4" s="52" t="n">
-        <v>0.1117182049427388</v>
+        <v>0.1116340473844373</v>
       </c>
       <c r="D4" s="52" t="n">
-        <v>0.1167182049427388</v>
+        <v>0.1166340473844373</v>
       </c>
       <c r="E4" s="52" t="n">
-        <v>0.1217182049427388</v>
+        <v>0.1216340473844373</v>
       </c>
       <c r="F4" s="52" t="n">
-        <v>0.1267182049427387</v>
+        <v>0.1266340473844373</v>
       </c>
       <c r="G4" s="52" t="n">
-        <v>0.1317182049427388</v>
+        <v>0.1316340473844373</v>
       </c>
       <c r="H4" s="52" t="n">
-        <v>0.1367182049427388</v>
+        <v>0.1366340473844373</v>
       </c>
     </row>
     <row r="5">
@@ -1131,25 +1131,25 @@
         <v>10</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>181.1792329651669</v>
+        <v>163.9285336976612</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>174.8773219419295</v>
+        <v>158.3248774443622</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>168.8540490318302</v>
+        <v>152.9677512915604</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>163.0954894313658</v>
+        <v>147.8448618377013</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>157.5884823328509</v>
+        <v>142.9445894233723</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>152.3205855531288</v>
+        <v>138.2559481444768</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>147.2800330529021</v>
+        <v>133.7685484120568</v>
       </c>
     </row>
     <row r="6">
@@ -1157,25 +1157,25 @@
         <v>11</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>190.9749857547231</v>
+        <v>172.5438607047444</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>184.2413171048008</v>
+        <v>166.5604471065959</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>177.8071275723472</v>
+        <v>160.8418959057764</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>171.657399711543</v>
+        <v>155.3749525130769</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>165.7779418598049</v>
+        <v>150.147090439248</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>160.1553390200845</v>
+        <v>145.146468012006</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>154.7769068761177</v>
+        <v>140.3618878529131</v>
       </c>
     </row>
     <row r="7">
@@ -1183,25 +1183,25 @@
         <v>12</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>200.7707385442794</v>
+        <v>181.1591877118277</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>193.605312267672</v>
+        <v>174.7960167688295</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>186.7602061128642</v>
+        <v>168.7160405199923</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>180.2193099917203</v>
+        <v>162.9050431884527</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>173.967401386759</v>
+        <v>157.3495914551237</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>167.9900924870401</v>
+        <v>152.0369878795351</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>162.2737806993332</v>
+        <v>146.9552272937695</v>
       </c>
     </row>
     <row r="8">
@@ -1209,25 +1209,25 @@
         <v>13</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>210.5664913338355</v>
+        <v>189.774514718911</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>202.9693074305432</v>
+        <v>183.0315864310632</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>195.7132846533813</v>
+        <v>176.5901851342083</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>188.7812202718975</v>
+        <v>170.4351338638284</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>182.1568609137131</v>
+        <v>164.5520924709994</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>175.8248459539958</v>
+        <v>158.9275077470643</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>169.7706545225488</v>
+        <v>153.5485667346259</v>
       </c>
     </row>
     <row r="9">
@@ -1235,25 +1235,25 @@
         <v>14</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>220.3622441233917</v>
+        <v>198.3898417259942</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>212.3333025934145</v>
+        <v>191.2671560932968</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>204.6663631938983</v>
+        <v>184.4643297484243</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>197.3431305520747</v>
+        <v>177.9652245392041</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>190.3463204406672</v>
+        <v>171.7545934868751</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>183.6595994209515</v>
+        <v>165.8180276145934</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>177.2675283457643</v>
+        <v>160.1419061754823</v>
       </c>
     </row>
     <row r="10">
@@ -1261,25 +1261,25 @@
         <v>15</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>230.157996912948</v>
+        <v>207.0051687330775</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>221.6972977562856</v>
+        <v>199.5027257555304</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>213.6194417344153</v>
+        <v>192.3384743626403</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>205.9050408322519</v>
+        <v>185.4953152145798</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>198.5357799676213</v>
+        <v>178.9570945027508</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>191.4943528879072</v>
+        <v>172.7085474821226</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>184.7644021689799</v>
+        <v>166.7352456163387</v>
       </c>
     </row>
     <row r="11">
@@ -1287,25 +1287,25 @@
         <v>16</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>239.9537497025042</v>
+        <v>215.6204957401607</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>231.0612929191569</v>
+        <v>207.7382954177641</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>222.5725202749324</v>
+        <v>200.2126189768563</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>214.4669511124291</v>
+        <v>193.0254058899555</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>206.7252394945754</v>
+        <v>186.1595955186266</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>199.3291063548628</v>
+        <v>179.5990673496517</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>192.2612759921954</v>
+        <v>173.3285850571951</v>
       </c>
     </row>
     <row r="13">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>603.0399780273438</v>
+        <v>551.2050170898438</v>
       </c>
     </row>
     <row r="14">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="B14" s="56" t="n">
-        <v>0.1217182049427388</v>
+        <v>0.1216340473844373</v>
       </c>
       <c r="C14" s="57" t="n">
         <v>13</v>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.9768232781557669</v>
+        <v>0.9777852543554396</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24410,7 +24410,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>603.0399780273438</v>
+        <v>551.2050170898438</v>
       </c>
     </row>
     <row r="49">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24572,13 +24572,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>188.7812202718975</v>
+        <v>170.4351338638284</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>256.4630962120982</v>
+        <v>225.9553441829456</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>137.8028015216592</v>
+        <v>127.4613434371423</v>
       </c>
     </row>
     <row r="59">
